--- a/Sender Gmail Emails/Datos/Asis_curso.xlsx
+++ b/Sender Gmail Emails/Datos/Asis_curso.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edgau\OneDrive\Documentos\GitHub\Python\Sender Gmail Emails\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cinvestav365-my.sharepoint.com/personal/edgar_agustin_cinvestav_mx/Documents/Documentos/GitHub/Python/Sender Gmail Emails/Datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD9760BC-8199-4F83-9FE3-50A275319245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{DD9760BC-8199-4F83-9FE3-50A275319245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE5541D4-2E45-44CD-AB06-4B1029A5FAE3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{57CD9F27-ED92-4D92-97BD-4EB2C2546C2C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{57CD9F27-ED92-4D92-97BD-4EB2C2546C2C}"/>
   </bookViews>
   <sheets>
     <sheet name="Asis_curso" sheetId="1" r:id="rId1"/>
@@ -2974,48 +2974,48 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Bueno" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Cálculo" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Celda de comprobación" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Celda vinculada" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Encabezado 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Encabezado 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Énfasis1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Énfasis2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Énfasis3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Énfasis4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Énfasis5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Énfasis6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Incorrecto" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Notas" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Salida" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Texto de advertencia" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Texto explicativo" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Título" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Título 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3031,7 +3031,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3348,13 +3348,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B35E6767-67BF-4C43-BB50-257DECA7AA9D}">
   <dimension ref="A1:M1048573"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="4" max="4" width="40.5703125" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" customWidth="1"/>
+    <col min="4" max="4" width="40.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3392,7 +3393,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46058.681250000001</v>
       </c>
@@ -3412,7 +3413,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46045.55</v>
       </c>
@@ -3432,7 +3433,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46055.72152777778</v>
       </c>
@@ -3455,7 +3456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46045.674305555556</v>
       </c>
@@ -3475,7 +3476,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46267.284722222219</v>
       </c>
@@ -3495,7 +3496,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>33</v>
       </c>
@@ -3512,7 +3513,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46045.48541666667</v>
       </c>
@@ -3532,7 +3533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>40</v>
       </c>
@@ -3552,7 +3553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46046.48541666667</v>
       </c>
@@ -3575,7 +3576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46045.727777777778</v>
       </c>
@@ -3598,7 +3599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46046.727777777778</v>
       </c>
@@ -3621,7 +3622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46045.481249999997</v>
       </c>
@@ -3641,7 +3642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46045.481944444444</v>
       </c>
@@ -3661,7 +3662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>62</v>
       </c>
@@ -3678,7 +3679,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46045.51666666667</v>
       </c>
@@ -3701,7 +3702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46045.981249999997</v>
       </c>
@@ -3718,7 +3719,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46046.447916666664</v>
       </c>
@@ -3741,7 +3742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46056.543055555558</v>
       </c>
@@ -3761,7 +3762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46053.90625</v>
       </c>
@@ -3784,7 +3785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46058.82916666667</v>
       </c>
@@ -3807,7 +3808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46268.375694444447</v>
       </c>
@@ -3830,7 +3831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46053.855555555558</v>
       </c>
@@ -3847,7 +3848,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46058.90902777778</v>
       </c>
@@ -3870,7 +3871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46056.462500000001</v>
       </c>
@@ -3890,7 +3891,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46061.008333333331</v>
       </c>
@@ -3910,7 +3911,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46045.481249999997</v>
       </c>
@@ -3930,7 +3931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46058.623611111114</v>
       </c>
@@ -3950,7 +3951,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>46236.984027777777</v>
       </c>
@@ -3970,7 +3971,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>113</v>
       </c>
@@ -3987,7 +3988,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>46053.932638888888</v>
       </c>
@@ -4004,7 +4005,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>46061.009722222225</v>
       </c>
@@ -4027,7 +4028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>46047.7</v>
       </c>
@@ -4050,7 +4051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>46058.683333333334</v>
       </c>
@@ -4073,7 +4074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>46046.398611111108</v>
       </c>
@@ -4093,7 +4094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>46053.84375</v>
       </c>
@@ -4113,7 +4114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>46054.723611111112</v>
       </c>
@@ -4133,7 +4134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>46058.645833333336</v>
       </c>
@@ -4150,7 +4151,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>143</v>
       </c>
@@ -4167,7 +4168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>46045.477777777778</v>
       </c>
@@ -4187,7 +4188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>46056.531944444447</v>
       </c>
@@ -4207,7 +4208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>46048.751388888886</v>
       </c>
@@ -4227,7 +4228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>46267.224999999999</v>
       </c>
@@ -4247,7 +4248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>46045.481249999997</v>
       </c>
@@ -4267,7 +4268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>46061.975694444445</v>
       </c>
@@ -4287,7 +4288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>46267.375694444447</v>
       </c>
@@ -4304,7 +4305,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46054.85</v>
       </c>
@@ -4321,7 +4322,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46267.375694444447</v>
       </c>
@@ -4338,7 +4339,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>46048.472222222219</v>
       </c>
@@ -4355,7 +4356,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>46053.932638888888</v>
       </c>
@@ -4375,7 +4376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>46046.425000000003</v>
       </c>
@@ -4395,7 +4396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>46045.482638888891</v>
       </c>
@@ -4415,7 +4416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>46053.886805555558</v>
       </c>
@@ -4432,7 +4433,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>46048.505555555559</v>
       </c>
@@ -4452,7 +4453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>46058.695833333331</v>
       </c>
@@ -4472,7 +4473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>46061.861805555556</v>
       </c>
@@ -4492,7 +4493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>46053.8125</v>
       </c>
@@ -4512,7 +4513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>46058.823611111111</v>
       </c>
@@ -4532,7 +4533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>46045.487500000003</v>
       </c>
@@ -4552,7 +4553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>46048.363888888889</v>
       </c>
@@ -4569,7 +4570,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>199</v>
       </c>
@@ -4583,7 +4584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>46059.090277777781</v>
       </c>
@@ -4600,7 +4601,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>46046.707638888889</v>
       </c>
@@ -4617,7 +4618,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>46054.154166666667</v>
       </c>
@@ -4637,7 +4638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>46045.484027777777</v>
       </c>
@@ -4657,7 +4658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>46061.972916666666</v>
       </c>
@@ -4677,7 +4678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>46045.51458333333</v>
       </c>
@@ -4694,7 +4695,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>46060.899305555555</v>
       </c>
@@ -4714,7 +4715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>46045.590277777781</v>
       </c>
@@ -4731,7 +4732,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>46058.524305555555</v>
       </c>
@@ -4748,7 +4749,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
         <v>228</v>
       </c>
@@ -4765,7 +4766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>46045.750694444447</v>
       </c>
@@ -4782,7 +4783,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>46058.859722222223</v>
       </c>
@@ -4802,7 +4803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>46053.814583333333</v>
       </c>
@@ -4819,7 +4820,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>46045.5</v>
       </c>
@@ -4839,7 +4840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>46053.893055555556</v>
       </c>
@@ -4859,7 +4860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
         <v>246</v>
       </c>
@@ -4873,7 +4874,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>46045.498611111114</v>
       </c>
@@ -4893,7 +4894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>46058.416666666664</v>
       </c>
@@ -4913,7 +4914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>46058.524305555555</v>
       </c>
@@ -4933,7 +4934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>46057.824305555558</v>
       </c>
@@ -4950,7 +4951,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>46045.477083333331</v>
       </c>
@@ -4970,7 +4971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B83" t="s">
         <v>264</v>
       </c>
@@ -4987,7 +4988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>46045.525000000001</v>
       </c>
@@ -5007,7 +5008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>46047.906944444447</v>
       </c>
@@ -5024,7 +5025,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>46045.482638888891</v>
       </c>
@@ -5041,7 +5042,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>46061.072916666664</v>
       </c>
@@ -5058,7 +5059,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>46061.442361111112</v>
       </c>
@@ -5078,7 +5079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>46267.022222222222</v>
       </c>
@@ -5095,7 +5096,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>46053.87222222222</v>
       </c>
@@ -5115,7 +5116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>46271.375694444447</v>
       </c>
@@ -5135,7 +5136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>46045.477777777778</v>
       </c>
@@ -5152,7 +5153,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>46045.486111111109</v>
       </c>
@@ -5169,7 +5170,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>46059.474999999999</v>
       </c>
@@ -5189,7 +5190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>46061.685416666667</v>
       </c>
@@ -5209,7 +5210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>46049.453472222223</v>
       </c>
@@ -5229,7 +5230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B97" t="s">
         <v>305</v>
       </c>
@@ -5243,7 +5244,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>46054.569444444445</v>
       </c>
@@ -5260,7 +5261,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>46061.363888888889</v>
       </c>
@@ -5277,7 +5278,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
         <v>315</v>
       </c>
@@ -5291,7 +5292,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>46052.765277777777</v>
       </c>
@@ -5308,7 +5309,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>46052.348611111112</v>
       </c>
@@ -5325,7 +5326,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>46045.477083333331</v>
       </c>
@@ -5342,7 +5343,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>46058.405555555553</v>
       </c>
@@ -5362,7 +5363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>46057.443749999999</v>
       </c>
@@ -5382,7 +5383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B106" t="s">
         <v>332</v>
       </c>
@@ -5399,7 +5400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>46045.520138888889</v>
       </c>
@@ -5416,7 +5417,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>46045.540972222225</v>
       </c>
@@ -5436,7 +5437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>46055.317361111112</v>
       </c>
@@ -5453,7 +5454,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>46045.548611111109</v>
       </c>
@@ -5473,7 +5474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>46054.724999999999</v>
       </c>
@@ -5493,7 +5494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>46061.609027777777</v>
       </c>
@@ -5510,7 +5511,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>46053.814583333333</v>
       </c>
@@ -5527,7 +5528,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B114" t="s">
         <v>353</v>
       </c>
@@ -5547,7 +5548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B115" t="s">
         <v>356</v>
       </c>
@@ -5564,7 +5565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>46045.481249999997</v>
       </c>
@@ -5584,7 +5585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>46269.375694444447</v>
       </c>
@@ -5604,7 +5605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>46053.88958333333</v>
       </c>
@@ -5621,7 +5622,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>46046.333333333336</v>
       </c>
@@ -5638,7 +5639,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>46061.563888888886</v>
       </c>
@@ -5658,7 +5659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>46058.525000000001</v>
       </c>
@@ -5675,7 +5676,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>46272.375694444447</v>
       </c>
@@ -5692,7 +5693,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>46045.810416666667</v>
       </c>
@@ -5709,7 +5710,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>46273.375694444447</v>
       </c>
@@ -5729,7 +5730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>46053.8125</v>
       </c>
@@ -5746,7 +5747,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B126" t="s">
         <v>386</v>
       </c>
@@ -5760,7 +5761,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>46057.667361111111</v>
       </c>
@@ -5777,7 +5778,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>46275.375694444447</v>
       </c>
@@ -5797,7 +5798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>46061.979166666664</v>
       </c>
@@ -5814,7 +5815,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>46045.479166666664</v>
       </c>
@@ -5831,7 +5832,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>46048.508333333331</v>
       </c>
@@ -5851,7 +5852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>46058.782638888886</v>
       </c>
@@ -5871,7 +5872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>46061.915972222225</v>
       </c>
@@ -5888,7 +5889,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>46058.586805555555</v>
       </c>
@@ -5908,7 +5909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>46054.70416666667</v>
       </c>
@@ -5928,7 +5929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>46056.484027777777</v>
       </c>
@@ -5948,7 +5949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>46045.490972222222</v>
       </c>
@@ -5965,7 +5966,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>46045.760416666664</v>
       </c>
@@ -5985,7 +5986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B139" t="s">
         <v>423</v>
       </c>
@@ -5999,7 +6000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B140" t="s">
         <v>427</v>
       </c>
@@ -6016,7 +6017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>46058.65347222222</v>
       </c>
@@ -6036,7 +6037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>46057.720833333333</v>
       </c>
@@ -6053,7 +6054,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>46045.477083333331</v>
       </c>
@@ -6070,7 +6071,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>46050.434027777781</v>
       </c>
@@ -6090,7 +6091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>46053.90347222222</v>
       </c>
@@ -6113,7 +6114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>46060.9</v>
       </c>
@@ -6133,7 +6134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>46054.001388888886</v>
       </c>
@@ -6153,7 +6154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>46061.070833333331</v>
       </c>
@@ -6170,7 +6171,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>46059.894444444442</v>
       </c>
@@ -6187,7 +6188,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>46058.52847222222</v>
       </c>
@@ -6207,7 +6208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>46057.681944444441</v>
       </c>
@@ -6224,7 +6225,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>46050.825694444444</v>
       </c>
@@ -6244,7 +6245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>46058.631249999999</v>
       </c>
@@ -6264,7 +6265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>46046.84652777778</v>
       </c>
@@ -6281,7 +6282,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>46045.665277777778</v>
       </c>
@@ -6301,7 +6302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>46061.665277777778</v>
       </c>
@@ -6318,7 +6319,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B157" t="s">
         <v>478</v>
       </c>
@@ -6335,7 +6336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>46060.944444444445</v>
       </c>
@@ -6355,7 +6356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>46053.925694444442</v>
       </c>
@@ -6375,7 +6376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>46049.59097222222</v>
       </c>
@@ -6392,7 +6393,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>46058.714583333334</v>
       </c>
@@ -6412,7 +6413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B162" t="s">
         <v>493</v>
       </c>
@@ -6429,7 +6430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>46061.913888888892</v>
       </c>
@@ -6449,7 +6450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>46054.587500000001</v>
       </c>
@@ -6466,7 +6467,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B165" t="s">
         <v>502</v>
       </c>
@@ -6483,7 +6484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B166" t="s">
         <v>505</v>
       </c>
@@ -6500,7 +6501,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>46267.45</v>
       </c>
@@ -6517,7 +6518,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>46054.402777777781</v>
       </c>
@@ -6534,7 +6535,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>46058.525000000001</v>
       </c>
@@ -6551,7 +6552,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>46045.490972222222</v>
       </c>
@@ -6571,7 +6572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>46047.944444444445</v>
       </c>
@@ -6591,7 +6592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>46049.425694444442</v>
       </c>
@@ -6611,7 +6612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B173" t="s">
         <v>522</v>
       </c>
@@ -6625,7 +6626,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>46061.645138888889</v>
       </c>
@@ -6642,7 +6643,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>46045.509722222225</v>
       </c>
@@ -6659,7 +6660,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B176" t="s">
         <v>531</v>
       </c>
@@ -6676,7 +6677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>46061.477777777778</v>
       </c>
@@ -6696,7 +6697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>46045.495138888888</v>
       </c>
@@ -6716,7 +6717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>46058.535416666666</v>
       </c>
@@ -6736,7 +6737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>46045.53402777778</v>
       </c>
@@ -6753,7 +6754,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>46057.427777777775</v>
       </c>
@@ -6770,7 +6771,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>46054.956250000003</v>
       </c>
@@ -6787,7 +6788,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>46045.482638888891</v>
       </c>
@@ -6807,7 +6808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>46047.510416666664</v>
       </c>
@@ -6824,7 +6825,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>46048.482638888891</v>
       </c>
@@ -6841,7 +6842,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>46053.886111111111</v>
       </c>
@@ -6858,7 +6859,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>46061.354166666664</v>
       </c>
@@ -6878,7 +6879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>46053.816666666666</v>
       </c>
@@ -6898,7 +6899,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>46053.947916666664</v>
       </c>
@@ -6915,7 +6916,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>46061.054861111108</v>
       </c>
@@ -6935,7 +6936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>46058.520833333336</v>
       </c>
@@ -6952,7 +6953,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>46058.537499999999</v>
       </c>
@@ -6972,7 +6973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>46046.049305555556</v>
       </c>
@@ -6989,7 +6990,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>46270.375694444447</v>
       </c>
@@ -7006,7 +7007,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>46267.304861111108</v>
       </c>
@@ -7026,7 +7027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>46053.940972222219</v>
       </c>
@@ -7043,7 +7044,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>46059.446527777778</v>
       </c>
@@ -7063,7 +7064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>46061.826388888891</v>
       </c>
@@ -7083,7 +7084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>46053.894444444442</v>
       </c>
@@ -7103,7 +7104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>46058.756249999999</v>
       </c>
@@ -7120,7 +7121,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>46059.551388888889</v>
       </c>
@@ -7140,7 +7141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>46061.82708333333</v>
       </c>
@@ -7160,7 +7161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>46061.97152777778</v>
       </c>
@@ -7180,7 +7181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>46058.798611111109</v>
       </c>
@@ -7200,7 +7201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>46045.5</v>
       </c>
@@ -7220,7 +7221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>46061.47152777778</v>
       </c>
@@ -7237,7 +7238,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>46053.481249999997</v>
       </c>
@@ -7254,7 +7255,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>46045.490277777775</v>
       </c>
@@ -7274,7 +7275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B209" t="s">
         <v>629</v>
       </c>
@@ -7291,7 +7292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>46045.722222222219</v>
       </c>
@@ -7308,7 +7309,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>46045.496527777781</v>
       </c>
@@ -7325,7 +7326,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>46045.481249999997</v>
       </c>
@@ -7345,7 +7346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>46061.01458333333</v>
       </c>
@@ -7362,7 +7363,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>46054.102777777778</v>
       </c>
@@ -7379,7 +7380,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B215" t="s">
         <v>647</v>
       </c>
@@ -7393,7 +7394,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>46274.375694444447</v>
       </c>
@@ -7413,7 +7414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>46048.520138888889</v>
       </c>
@@ -7433,7 +7434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>46058.523611111108</v>
       </c>
@@ -7456,7 +7457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>46048.508333333331</v>
       </c>
@@ -7479,7 +7480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>46056.454861111109</v>
       </c>
@@ -7502,7 +7503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>46059.527083333334</v>
       </c>
@@ -7522,7 +7523,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>46058.688194444447</v>
       </c>
@@ -7539,7 +7540,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>46045.498611111114</v>
       </c>
@@ -7562,7 +7563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>46058.897916666669</v>
       </c>
@@ -7585,7 +7586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>46046.476388888892</v>
       </c>
@@ -7605,7 +7606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>46045.477777777778</v>
       </c>
@@ -7622,7 +7623,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>46045.50277777778</v>
       </c>
@@ -7642,7 +7643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>46058.656944444447</v>
       </c>
@@ -7662,7 +7663,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B229" t="s">
         <v>693</v>
       </c>
@@ -7682,7 +7683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>46267.276388888888</v>
       </c>
@@ -7705,7 +7706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>46059.396527777775</v>
       </c>
@@ -7725,7 +7726,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>46045.486111111109</v>
       </c>
@@ -7745,7 +7746,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>46045.484027777777</v>
       </c>
@@ -7765,7 +7766,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>46047.488888888889</v>
       </c>
@@ -7785,7 +7786,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>46053.929861111108</v>
       </c>
@@ -7808,7 +7809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>46058.978472222225</v>
       </c>
@@ -7831,7 +7832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>46058.655555555553</v>
       </c>
@@ -7851,7 +7852,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>46267.370138888888</v>
       </c>
@@ -7871,7 +7872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>46057.644444444442</v>
       </c>
@@ -7894,7 +7895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>46058.65625</v>
       </c>
@@ -7917,7 +7918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>46055.651388888888</v>
       </c>
@@ -7940,7 +7941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>46058.657638888886</v>
       </c>
@@ -7960,7 +7961,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B243" t="s">
         <v>742</v>
       </c>
@@ -7974,7 +7975,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B244" t="s">
         <v>745</v>
       </c>
@@ -7988,7 +7989,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>46236.995138888888</v>
       </c>
@@ -8011,7 +8012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>46045.486805555556</v>
       </c>
@@ -8034,7 +8035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>46045.48333333333</v>
       </c>
@@ -8054,7 +8055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>46045.874305555553</v>
       </c>
@@ -8074,7 +8075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>46045.741666666669</v>
       </c>
@@ -8097,7 +8098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>46056.272916666669</v>
       </c>
@@ -8117,7 +8118,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B251" t="s">
         <v>768</v>
       </c>
@@ -8137,7 +8138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>46060.165972222225</v>
       </c>
@@ -8160,7 +8161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>46049.572916666664</v>
       </c>
@@ -8177,7 +8178,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>46053.948611111111</v>
       </c>
@@ -8197,7 +8198,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>46058.525694444441</v>
       </c>
@@ -8220,7 +8221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B256" t="s">
         <v>786</v>
       </c>
@@ -8243,7 +8244,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>46053.813194444447</v>
       </c>
@@ -8266,7 +8267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>46061.484027777777</v>
       </c>
@@ -8289,7 +8290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>46060.685416666667</v>
       </c>
@@ -8312,7 +8313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>46058.661111111112</v>
       </c>
@@ -8335,7 +8336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>46053.862500000003</v>
       </c>
@@ -8358,7 +8359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>46060.566666666666</v>
       </c>
@@ -8381,7 +8382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>46061.265972222223</v>
       </c>
@@ -8404,7 +8405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B264" t="s">
         <v>814</v>
       </c>
@@ -8424,7 +8425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B265" t="s">
         <v>225</v>
       </c>
@@ -8444,7 +8445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B266" t="s">
         <v>276</v>
       </c>
@@ -8464,7 +8465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1048573" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="1048573" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E1048573" t="s">
         <v>23</v>
       </c>
